--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_nuble.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_nuble.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>26.42890921840092</v>
+      </c>
+      <c r="C2">
         <v>28.02455848539699</v>
-      </c>
-      <c r="C2">
-        <v>26.42890921840092</v>
       </c>
       <c r="D2">
         <v>3.568298856594222</v>
       </c>
       <c r="E2">
-        <v>18.14433751603486</v>
+        <v>17.1112436718383</v>
       </c>
       <c r="F2">
         <v>64.74441881212685</v>
       </c>
       <c r="G2">
-        <v>17.1112436718383</v>
+        <v>18.14433751603486</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>28.42782759618166</v>
+      </c>
+      <c r="C3">
         <v>33.72866647382124</v>
-      </c>
-      <c r="C3">
-        <v>28.42782759618166</v>
       </c>
       <c r="D3">
         <v>2.96483704974271</v>
       </c>
       <c r="E3">
-        <v>20.80007135530482</v>
+        <v>17.53110645319538</v>
       </c>
       <c r="F3">
         <v>61.66882219149979</v>
       </c>
       <c r="G3">
-        <v>17.53110645319538</v>
+        <v>20.80007135530482</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>29.76275328377966</v>
+      </c>
+      <c r="C4">
         <v>22.73699215965788</v>
-      </c>
-      <c r="C4">
-        <v>29.76275328377966</v>
       </c>
       <c r="D4">
         <v>4.398119122257054</v>
       </c>
       <c r="E4">
+        <v>19.51659210789878</v>
+      </c>
+      <c r="F4">
+        <v>65.57387994925551</v>
+      </c>
+      <c r="G4">
         <v>14.9095279428457</v>
-      </c>
-      <c r="F4">
-        <v>65.57387994925553</v>
-      </c>
-      <c r="G4">
-        <v>19.51659210789878</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>29.74422442244224</v>
+      </c>
+      <c r="C5">
         <v>35.25852585258526</v>
-      </c>
-      <c r="C5">
-        <v>29.74422442244224</v>
       </c>
       <c r="D5">
         <v>2.83619344773791</v>
       </c>
       <c r="E5">
-        <v>21.36844737061422</v>
+        <v>18.02650220851738</v>
       </c>
       <c r="F5">
         <v>60.60505042086841</v>
       </c>
       <c r="G5">
-        <v>18.02650220851738</v>
+        <v>21.36844737061422</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>30.09503695881732</v>
+      </c>
+      <c r="C6">
         <v>34.29778247096093</v>
-      </c>
-      <c r="C6">
-        <v>30.09503695881732</v>
       </c>
       <c r="D6">
         <v>2.91564039408867</v>
       </c>
       <c r="E6">
+        <v>18.30678314491264</v>
+      </c>
+      <c r="F6">
+        <v>60.82990750256937</v>
+      </c>
+      <c r="G6">
         <v>20.86330935251799</v>
-      </c>
-      <c r="F6">
-        <v>60.82990750256938</v>
-      </c>
-      <c r="G6">
-        <v>18.30678314491264</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>26.0177236222653</v>
+      </c>
+      <c r="C7">
         <v>35.14261977291609</v>
-      </c>
-      <c r="C7">
-        <v>26.0177236222653</v>
       </c>
       <c r="D7">
         <v>2.84554767533491</v>
       </c>
       <c r="E7">
-        <v>21.80599707878684</v>
+        <v>16.14399862531145</v>
       </c>
       <c r="F7">
         <v>62.05000429590172</v>
       </c>
       <c r="G7">
-        <v>16.14399862531145</v>
+        <v>21.80599707878684</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>27.74021521759832</v>
+      </c>
+      <c r="C8">
         <v>40.21521759832397</v>
-      </c>
-      <c r="C8">
-        <v>27.74021521759832</v>
       </c>
       <c r="D8">
         <v>2.486620885626332</v>
       </c>
       <c r="E8">
+        <v>16.51641435618303</v>
+      </c>
+      <c r="F8">
+        <v>59.53960424108409</v>
+      </c>
+      <c r="G8">
         <v>23.94398140273289</v>
-      </c>
-      <c r="F8">
-        <v>59.53960424108408</v>
-      </c>
-      <c r="G8">
-        <v>16.51641435618302</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>28.72614196868969</v>
+      </c>
+      <c r="C9">
         <v>36.78962041604117</v>
-      </c>
-      <c r="C9">
-        <v>28.72614196868969</v>
       </c>
       <c r="D9">
         <v>2.718157971436899</v>
       </c>
       <c r="E9">
-        <v>22.22726094843224</v>
+        <v>17.3555325213786</v>
       </c>
       <c r="F9">
         <v>60.41720653018917</v>
       </c>
       <c r="G9">
-        <v>17.3555325213786</v>
+        <v>22.22726094843224</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>30.85011407598452</v>
+      </c>
+      <c r="C10">
         <v>34.86757266144232</v>
-      </c>
-      <c r="C10">
-        <v>30.85011407598452</v>
       </c>
       <c r="D10">
         <v>2.867994310099573</v>
       </c>
       <c r="E10">
-        <v>21.04034478630432</v>
+        <v>18.61606608404166</v>
       </c>
       <c r="F10">
         <v>60.34358912965401</v>
       </c>
       <c r="G10">
-        <v>18.61606608404166</v>
+        <v>21.04034478630432</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>26.98105379615544</v>
+      </c>
+      <c r="C11">
         <v>37.39455123772645</v>
-      </c>
-      <c r="C11">
-        <v>26.98105379615544</v>
       </c>
       <c r="D11">
         <v>2.674186390532544</v>
       </c>
       <c r="E11">
-        <v>22.74945313814572</v>
+        <v>16.41426888776712</v>
       </c>
       <c r="F11">
         <v>60.83627797408716</v>
       </c>
       <c r="G11">
-        <v>16.41426888776712</v>
+        <v>22.74945313814572</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>26.4171511627907</v>
+      </c>
+      <c r="C12">
         <v>49.05523255813954</v>
-      </c>
-      <c r="C12">
-        <v>26.4171511627907</v>
       </c>
       <c r="D12">
         <v>2.038518518518519</v>
       </c>
       <c r="E12">
-        <v>27.95609857113273</v>
+        <v>15.05487678608408</v>
       </c>
       <c r="F12">
-        <v>56.98902464278318</v>
+        <v>56.98902464278319</v>
       </c>
       <c r="G12">
-        <v>15.05487678608407</v>
+        <v>27.95609857113274</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>26.87289978256572</v>
+      </c>
+      <c r="C13">
         <v>37.13184423799169</v>
-      </c>
-      <c r="C13">
-        <v>26.87289978256572</v>
       </c>
       <c r="D13">
         <v>2.693106201756721</v>
       </c>
       <c r="E13">
-        <v>22.64071351090756</v>
+        <v>16.38544052067012</v>
       </c>
       <c r="F13">
         <v>60.97384596842232</v>
       </c>
       <c r="G13">
-        <v>16.38544052067012</v>
+        <v>22.64071351090756</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>26.2776025236593</v>
+      </c>
+      <c r="C14">
         <v>43.53312302839117</v>
-      </c>
-      <c r="C14">
-        <v>26.2776025236593</v>
       </c>
       <c r="D14">
         <v>2.297101449275362</v>
       </c>
       <c r="E14">
-        <v>25.6362623072636</v>
+        <v>15.47464239271781</v>
       </c>
       <c r="F14">
         <v>58.88909530001857</v>
       </c>
       <c r="G14">
-        <v>15.47464239271781</v>
+        <v>25.6362623072636</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>26.98737632207438</v>
+      </c>
+      <c r="C15">
         <v>43.87581030365063</v>
-      </c>
-      <c r="C15">
-        <v>26.98737632207438</v>
       </c>
       <c r="D15">
         <v>2.279160186625194</v>
       </c>
       <c r="E15">
-        <v>25.67891373801917</v>
+        <v>15.79472843450479</v>
       </c>
       <c r="F15">
         <v>58.52635782747604</v>
       </c>
       <c r="G15">
-        <v>15.79472843450479</v>
+        <v>25.67891373801917</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>30.33070866141732</v>
+      </c>
+      <c r="C16">
         <v>47.62204724409449</v>
-      </c>
-      <c r="C16">
-        <v>30.33070866141732</v>
       </c>
       <c r="D16">
         <v>2.099867724867725</v>
       </c>
       <c r="E16">
-        <v>26.76106194690265</v>
+        <v>17.04424778761062</v>
       </c>
       <c r="F16">
         <v>56.19469026548672</v>
       </c>
       <c r="G16">
-        <v>17.04424778761062</v>
+        <v>26.76106194690265</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>23.03096143400326</v>
+      </c>
+      <c r="C17">
         <v>34.70939706681151</v>
-      </c>
-      <c r="C17">
-        <v>23.03096143400326</v>
       </c>
       <c r="D17">
         <v>2.881064162754304</v>
       </c>
       <c r="E17">
+        <v>14.60055096418733</v>
+      </c>
+      <c r="F17">
+        <v>63.39531680440771</v>
+      </c>
+      <c r="G17">
         <v>22.00413223140496</v>
-      </c>
-      <c r="F17">
-        <v>63.39531680440772</v>
-      </c>
-      <c r="G17">
-        <v>14.60055096418733</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>27.60529840750112</v>
+      </c>
+      <c r="C18">
         <v>33.38889715731508</v>
-      </c>
-      <c r="C18">
-        <v>27.60529840750112</v>
       </c>
       <c r="D18">
         <v>2.995007577783721</v>
       </c>
       <c r="E18">
-        <v>20.73919313685612</v>
+        <v>17.14676626113967</v>
       </c>
       <c r="F18">
         <v>62.11404060200421</v>
       </c>
       <c r="G18">
-        <v>17.14676626113967</v>
+        <v>20.73919313685612</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>29.24088463837418</v>
+      </c>
+      <c r="C19">
         <v>27.70472205618649</v>
-      </c>
-      <c r="C19">
-        <v>29.24088463837418</v>
       </c>
       <c r="D19">
         <v>3.609492988133765</v>
       </c>
       <c r="E19">
-        <v>17.65243554099859</v>
+        <v>18.63122215028373</v>
       </c>
       <c r="F19">
         <v>63.71634230871768</v>
       </c>
       <c r="G19">
-        <v>18.63122215028373</v>
+        <v>17.65243554099859</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>20.94012046769812</v>
+      </c>
+      <c r="C20">
         <v>39.29372859336247</v>
-      </c>
-      <c r="C20">
-        <v>20.94012046769812</v>
       </c>
       <c r="D20">
         <v>2.544935377216712</v>
       </c>
       <c r="E20">
-        <v>24.52273899904179</v>
+        <v>13.06847497604481</v>
       </c>
       <c r="F20">
         <v>62.40878602491339</v>
       </c>
       <c r="G20">
-        <v>13.06847497604481</v>
+        <v>24.52273899904179</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>33.7248322147651</v>
+      </c>
+      <c r="C21">
         <v>42.1979865771812</v>
-      </c>
-      <c r="C21">
-        <v>33.7248322147651</v>
       </c>
       <c r="D21">
         <v>2.369781312127237</v>
       </c>
       <c r="E21">
-        <v>23.9866475917978</v>
+        <v>19.17024320457797</v>
       </c>
       <c r="F21">
         <v>56.84310920362422</v>
       </c>
       <c r="G21">
-        <v>19.17024320457797</v>
+        <v>23.9866475917978</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>25.42805100182149</v>
+      </c>
+      <c r="C22">
         <v>32.54401942926533</v>
-      </c>
-      <c r="C22">
-        <v>25.42805100182149</v>
       </c>
       <c r="D22">
         <v>3.072761194029851</v>
       </c>
       <c r="E22">
+        <v>16.09654854331617</v>
+      </c>
+      <c r="F22">
+        <v>63.30232915673764</v>
+      </c>
+      <c r="G22">
         <v>20.60112229994619</v>
-      </c>
-      <c r="F22">
-        <v>63.30232915673763</v>
-      </c>
-      <c r="G22">
-        <v>16.09654854331616</v>
       </c>
     </row>
   </sheetData>
